--- a/dat/insertiondata.xlsx
+++ b/dat/insertiondata.xlsx
@@ -8,21 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/estebanhernandez/Documents/Holy Cross College/CS-280-Projects/dat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{49B3D766-8ADA-6249-A23F-95D7967A5F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B886F210-2BE2-5B44-AD10-72278DA9C2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="1520" windowWidth="27640" windowHeight="16520" xr2:uid="{CB234998-6A62-CA47-8E21-EBFFA07D4368}"/>
+    <workbookView xWindow="1620" yWindow="940" windowWidth="27640" windowHeight="16520" xr2:uid="{CB234998-6A62-CA47-8E21-EBFFA07D4368}"/>
   </bookViews>
   <sheets>
     <sheet name="insertiondata" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">insertiondata!$A$19</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">insertiondata!$B$19</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">insertiondata!$B$1:$B$18</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">insertiondata!$A$19</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">insertiondata!$B$19</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">insertiondata!$B$1:$B$18</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -44,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="4" uniqueCount="4">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="6" uniqueCount="6">
   <si>
     <t>N</t>
   </si>
@@ -57,12 +49,18 @@
   <si>
     <t xml:space="preserve">Log T </t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,6 +194,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -539,9 +550,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -598,6 +611,1108 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.8540037989166888E-2"/>
+          <c:y val="0.11488549990730713"/>
+          <c:w val="0.93046855184619459"/>
+          <c:h val="0.85103767233556771"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Log data</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>insertiondata!$D$2:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4771212547196624</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6020599913279623</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.6989700043360187</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7781512503836436</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.8450980400142569</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.9030899869919435</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.954242509439325</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.0413926851582249</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0791812460476247</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.1139433523068369</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1461280356782382</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.1760912590556813</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.2041199826559246</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2304489213782741</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2787536009528289</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>insertiondata!$E$2:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>-5.2341080235699842</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.7367427729859335</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.6717835424992824</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.5948757110728504</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.5646334933873387</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.43130557259716</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.4056958646252662</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.24096706677574</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-5.3194831906187448</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.1627272974976997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.8131848755525457</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-4.5326435177621018</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.3407971225354691</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.1728440489402798</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.0897278686046867</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.9996396850900315</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-3.8764227369394209</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.5783960731301687</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.378987388729179</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.65447102723456441</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0DD0-114C-9541-F55C770E04E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>AL</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.12592211128191211"/>
+                  <c:y val="-0.16638496142802117"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65%"/>
+                          <a:lumOff val="35%"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>insertiondata!$F$2:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>insertiondata!$G$2:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0DD0-114C-9541-F55C770E04E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="638358784"/>
+        <c:axId val="638356096"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="638358784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638356096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="638356096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="638358784"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15%"/>
+          <a:lumOff val="85%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+    <a:lumOff val="20%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+    <a:lumOff val="40%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+    <a:lumOff val="30%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+    <a:lumOff val="50%"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75%"/>
+        <a:lumOff val="25%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75%"/>
+          <a:lumOff val="25%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5%"/>
+            <a:lumOff val="95%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50%"/>
+            <a:lumOff val="50%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0%"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>162560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>142240</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBAF6DAA-98E4-94E7-D163-15D05F1A3E86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://purl.oclc.org/ooxml/drawingml/chart">
+          <c:chart xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -917,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAE749A-1801-4546-8654-29F3298475ED}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -925,7 +2040,7 @@
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -938,8 +2053,14 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>10</v>
       </c>
@@ -954,24 +2075,23 @@
         <f>LOG(B2)</f>
         <v>-5.2341080235699842</v>
       </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1">
-        <v>8.5419999999999998</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D19" si="0">LOG(A3)</f>
-        <v>1.3010299956639813</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E19" si="1">LOG(B3)</f>
-        <v>0.93155956709080523</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="1"/>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>-5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>30</v>
       </c>
@@ -979,15 +2099,15 @@
         <v>1.8334000000000001E-5</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D3:D22" si="0">LOG(A4)</f>
         <v>1.4771212547196624</v>
       </c>
       <c r="E4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E3:E22" si="1">LOG(B4)</f>
         <v>-4.7367427729859335</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>40</v>
       </c>
@@ -1003,7 +2123,7 @@
         <v>-4.6717835424992824</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>50</v>
       </c>
@@ -1019,7 +2139,7 @@
         <v>-4.5948757110728504</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>60</v>
       </c>
@@ -1035,7 +2155,7 @@
         <v>-4.5646334933873387</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>70</v>
       </c>
@@ -1051,7 +2171,7 @@
         <v>-4.43130557259716</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>80</v>
       </c>
@@ -1067,7 +2187,7 @@
         <v>-4.4056958646252662</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>90</v>
       </c>
@@ -1083,7 +2203,7 @@
         <v>-4.24096706677574</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>100</v>
       </c>
@@ -1099,7 +2219,7 @@
         <v>-5.3194831906187448</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>110</v>
       </c>
@@ -1115,7 +2235,7 @@
         <v>-5.1627272974976997</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>120</v>
       </c>
@@ -1131,7 +2251,7 @@
         <v>-4.8131848755525457</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>130</v>
       </c>
@@ -1147,7 +2267,7 @@
         <v>-4.5326435177621018</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>140</v>
       </c>
@@ -1163,7 +2283,7 @@
         <v>-4.3407971225354691</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>150</v>
       </c>
@@ -1227,7 +2347,56 @@
         <v>-3.8764227369394209</v>
       </c>
     </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2.64E-3</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>-2.5783960731301687</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="3">
+        <v>4.1784250000000002E-2</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>-1.378987388729179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4.5130591669999998</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>0.65447102723456441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>